--- a/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_vol/staggered_7d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_vol/staggered_7d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -468,16 +468,16 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.1007753032458945</v>
+        <v>0.04077492668478322</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1252615309008378</v>
+        <v>0.06392647425058784</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.317552144122787</v>
+        <v>0.2530428047058236</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2597542958862659</v>
+        <v>0.1872976056192806</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4529571999548628</v>
+        <v>0.2458197083546093</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.6555029812318562</v>
+        <v>0.3456560896316285</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.6446458969056015</v>
+        <v>0.4581741404298453</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.2245111420173688</v>
+        <v>0.1951857785134343</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1843860439966349</v>
+        <v>0.1174306782715099</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.5104690817750859</v>
+        <v>0.2366885689353791</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>23.34085595154166</v>
+        <v>26.59152308840194</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2029401301392623</v>
+        <v>-0.2081397044077866</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02923119965620646</v>
+        <v>0.02251706905641937</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2745726767838352</v>
+        <v>0.2432711934727878</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1858198052267632</v>
+        <v>0.1480430144792357</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.7772529000090151</v>
+        <v>-0.9381213221981216</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.058764859617174</v>
+        <v>-1.239695545076041</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.2468053986023746</v>
+        <v>0.2097758332368322</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2685300508517023</v>
+        <v>0.2591462749630896</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1517541911310614</v>
+        <v>0.1093631970261683</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.7834357169698534</v>
+        <v>-0.8324998267929278</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>23.86772699599252</v>
+        <v>24.89150661983494</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1920759227160947</v>
+        <v>-0.1659834144419907</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.08794689773324349</v>
+        <v>-0.05849146524096815</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2394677046802384</v>
+        <v>0.2039393986485948</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1767985156786583</v>
+        <v>0.1334737139332023</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.8701616908129801</v>
+        <v>-0.8979093478294679</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.231933425149013</v>
+        <v>-1.246441211739469</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.4321145524745462</v>
+        <v>-0.3831517053902841</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.303898779511344</v>
+        <v>0.2895778105250149</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.1616060714291134</v>
+        <v>0.1262437962193618</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.6553671955161519</v>
+        <v>-0.5947113434174065</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>27.07434859476112</v>
+        <v>26.89305840406847</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.08474250321667087</v>
+        <v>-0.02409198466718665</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.1898993613472746</v>
+        <v>-0.1362171746574853</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2931219397536329</v>
+        <v>0.2557291088863178</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1552847410121592</v>
+        <v>0.1262134476440086</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.2209253595512918</v>
+        <v>-0.03188561981839159</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.3423865720989023</v>
+        <v>-0.0517410575464077</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.30478348155752</v>
+        <v>-1.156841675321558</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2650910831352293</v>
+        <v>0.2590222763718885</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2194343989856963</v>
+        <v>0.2024306914890407</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.3322834803888598</v>
+        <v>-0.09680609911619173</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>26.11330284507153</v>
+        <v>26.55436185071294</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3150441994243809</v>
+        <v>0.2348487131984431</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.07410142571760803</v>
+        <v>0.008599379376425631</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2946495105261827</v>
+        <v>0.2237954602544589</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1764604126676318</v>
+        <v>0.1091204420852779</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.061057939268187</v>
+        <v>1.023552738059511</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.553621301637454</v>
+        <v>1.445887316732439</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.586646501823586</v>
+        <v>0.1827901086551047</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.178701615211787</v>
+        <v>0.1666106479749191</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.136453726157293</v>
+        <v>0.123042350898279</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.837985763292048</v>
+        <v>1.467698853566449</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>27.0091121980684</v>
+        <v>28.50206944386916</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.2029752500907667</v>
+        <v>0.2028845386152802</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2213460466743071</v>
+        <v>0.2212539499316957</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.3627470108818309</v>
+        <v>0.2894993053026522</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2336291786257372</v>
+        <v>0.167856186700266</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.07111577410055</v>
+        <v>1.258706860699278</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.501984691116342</v>
+        <v>1.790012273201517</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.732950543260989</v>
+        <v>2.268123301822017</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1297763042499026</v>
+        <v>0.1239765423065292</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09418772256956665</v>
+        <v>0.0755364292732783</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.092855085574445</v>
+        <v>3.235985891277697</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>23.9686759208154</v>
+        <v>27.18713070547772</v>
       </c>
     </row>
   </sheetData>
